--- a/data_lake/industry/TrendForce/Li-Ion Battery.xlsx
+++ b/data_lake/industry/TrendForce/Li-Ion Battery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1579F13-6501-4370-A3A8-E704A297C1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07596609-5EA9-4EAF-A6D2-C94B4060BF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Battery Cell &amp; Pack" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="71">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -260,6 +260,75 @@
   <si>
     <t>https://www.trendforce.com/price/battery-price/battery_cell_and_pack</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Electrolytic Cobalt: Co Content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>99.8% (10K RMB/ton) (RMB)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cobalt(II,III) Oxide: Co Content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>72.8% (10K RMB/ton) (RMB)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Battery-Grade Nickel Sulfate: Co Content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>20.5% (10K RMB/ton) (RMB)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -267,23 +336,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -296,7 +365,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -317,9 +386,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -341,77 +421,54 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -689,284 +746,319 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="25"/>
-    <col min="22" max="16384" width="9" style="24"/>
+    <col min="1" max="1" width="10.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="14"/>
+    <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="19" customFormat="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="20">
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>46028</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="9">
         <v>46028</v>
       </c>
-      <c r="C2" s="21">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="23">
+      <c r="C2" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12">
         <v>0.49</v>
       </c>
-      <c r="F2" s="23">
+      <c r="F2" s="12">
         <v>0.35</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="12">
         <v>0.52</v>
       </c>
-      <c r="H2" s="23">
+      <c r="H2" s="12">
         <v>0.33</v>
       </c>
-      <c r="I2" s="23">
+      <c r="I2" s="12">
         <v>7.63</v>
       </c>
-      <c r="J2" s="23">
+      <c r="J2" s="12">
         <v>0.65</v>
       </c>
-      <c r="K2" s="23">
+      <c r="K2" s="12">
         <v>0.46</v>
       </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="20">
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>46064</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="9">
         <v>46064</v>
       </c>
-      <c r="C3" s="21">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="23">
+      <c r="C3" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12">
         <v>0.52</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="12">
         <v>0.36</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="12">
         <v>0.34</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="12">
         <v>7.84</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="12">
         <v>0.67</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="12">
         <v>0.48</v>
       </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="20">
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>46090</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="9">
         <v>46090</v>
       </c>
-      <c r="C4" s="21">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="25">
+      <c r="C4" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="14">
         <v>0.56000000000000005</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="14">
         <v>0.37</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="14">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="14">
         <v>0.35</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="14">
         <v>8.2100000000000009</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="14">
         <v>0.7</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="14">
         <v>0.49</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="20">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>46125</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="9">
         <v>46125</v>
       </c>
-      <c r="C5" s="21">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="25">
+      <c r="C5" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="14">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="14">
         <v>0.38</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="14">
         <v>0.59</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="14">
         <v>0.35</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="14">
         <v>8.25</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="14">
         <v>0.72</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="20">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>46157</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="9">
         <v>46157</v>
       </c>
-      <c r="C6" s="21">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="25">
+      <c r="C6" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="14">
         <v>0.59</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="14">
         <v>0.38</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="14">
         <v>0.6</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="14">
         <v>0.36</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="14">
         <v>8.25</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="14">
         <v>0.74</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="20">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46178</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="9">
         <v>46178</v>
       </c>
-      <c r="C7" s="21">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="25">
+      <c r="C7" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="14">
         <v>0.6</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="14">
         <v>0.39</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="14">
         <v>0.61</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="14">
         <v>0.37</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="14">
         <v>8.32</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="14">
         <v>0.76</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="14">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0.39</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0.61</v>
+      </c>
+      <c r="H8" s="14">
+        <v>0.37</v>
+      </c>
+      <c r="I8" s="14">
+        <v>8.4</v>
+      </c>
+      <c r="J8" s="14">
+        <v>0.76</v>
+      </c>
+      <c r="K8" s="14">
         <v>0.51</v>
       </c>
     </row>
@@ -979,339 +1071,384 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93A7413-903B-41E3-BDE3-CD88FC030C93}">
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="7"/>
-    <col min="22" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="9.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="9.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="21" width="9" style="14"/>
+    <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14">
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>46028</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>46028</v>
       </c>
-      <c r="C2" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="12">
         <v>9.9499999999999993</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="12">
         <v>9.65</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="12">
         <v>10.88</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="12">
         <v>14.9</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="12">
         <v>15.2</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="12">
         <v>16.760000000000002</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="12">
         <v>4.16</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="12">
         <v>38.67</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="12">
         <v>4.12</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="14">
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>46064</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="9">
         <v>46064</v>
       </c>
-      <c r="C3" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12">
         <v>1.1499999999999999</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="12">
         <v>10.31</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="12">
         <v>10.01</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="12">
         <v>11.3</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="12">
         <v>16.579999999999998</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="12">
         <v>17.079999999999998</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="12">
         <v>18.47</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="12">
         <v>5.17</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="12">
         <v>40.56</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="12">
         <v>5.07</v>
       </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="14">
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>46090</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>46090</v>
       </c>
-      <c r="C4" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="7">
+      <c r="C4" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="14">
         <v>1.17</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="14">
         <v>10.6</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="14">
         <v>10.33</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="14">
         <v>11.73</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="14">
         <v>17.87</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="14">
         <v>18.25</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="14">
         <v>20.07</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="14">
         <v>5.41</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="14">
         <v>40.9</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="14">
         <v>5.29</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="14">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>46125</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>46125</v>
       </c>
-      <c r="C5" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="C5" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="14">
         <v>1.2</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="14">
         <v>10.59</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="14">
         <v>10.3</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="14">
         <v>11.73</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="14">
         <v>18.29</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="14">
         <v>18.53</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="14">
         <v>20.399999999999999</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="14">
         <v>5.55</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="14">
         <v>39.76</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="14">
         <v>5.54</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="14">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>46157</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>46157</v>
       </c>
-      <c r="C6" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="C6" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="14">
         <v>1.27</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="14">
         <v>10.57</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="14">
         <v>10.25</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="14">
         <v>11.76</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="14">
         <v>18.72</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="14">
         <v>18.920000000000002</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="14">
         <v>20.79</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="14">
         <v>5.71</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="14">
         <v>39.5</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="14">
         <v>5.72</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="14">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46178</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <v>46178</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="C7" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="14">
         <v>1.36</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="14">
         <v>10.71</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="14">
         <v>10.44</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="14">
         <v>12.03</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="14">
         <v>19.55</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="14">
         <v>19.82</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="14">
         <v>21.67</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="14">
         <v>6.4</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="14">
         <v>39.6</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="14">
         <v>6.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1.46</v>
+      </c>
+      <c r="F8" s="14">
+        <v>10.48</v>
+      </c>
+      <c r="G8" s="14">
+        <v>10.33</v>
+      </c>
+      <c r="H8" s="14">
+        <v>11.92</v>
+      </c>
+      <c r="I8" s="14">
+        <v>18.63</v>
+      </c>
+      <c r="J8" s="14">
+        <v>18.97</v>
+      </c>
+      <c r="K8" s="14">
+        <v>20.71</v>
+      </c>
+      <c r="L8" s="14">
+        <v>6.08</v>
+      </c>
+      <c r="M8" s="14">
+        <v>37.369999999999997</v>
+      </c>
+      <c r="N8" s="14">
+        <v>6.04</v>
       </c>
     </row>
   </sheetData>
@@ -1322,302 +1459,340 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0866DC8-FCF3-4C5E-83C2-1F3B814AC134}">
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="7"/>
-    <col min="22" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="9.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="14"/>
+    <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14">
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>46028</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>46028</v>
       </c>
-      <c r="C2" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12">
         <v>0.75</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="12">
         <v>0.9</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="12">
         <v>2.12</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="12">
         <v>2.67</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="12">
         <v>4.5199999999999996</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="12">
         <v>2.13</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="12">
         <v>2.95</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="12">
         <v>5.2</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="14">
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>46064</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="9">
         <v>46064</v>
       </c>
-      <c r="C3" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12">
         <v>0.75</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="12">
         <v>0.9</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="12">
         <v>2.12</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="12">
         <v>2.67</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="12">
         <v>4.5199999999999996</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="12">
         <v>2.13</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="12">
         <v>2.95</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="12">
         <v>5.2</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="14">
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>46090</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>46090</v>
       </c>
-      <c r="C4" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="12">
         <v>0.75</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="12">
         <v>0.9</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="12">
         <v>2.12</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="12">
         <v>2.67</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="12">
         <v>4.5199999999999996</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="12">
         <v>2.13</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="12">
         <v>2.95</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="12">
         <v>5.2</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="14">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>46125</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>46125</v>
       </c>
-      <c r="C5" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="C5" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="14">
         <v>0.75</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="14">
         <v>0.9</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="14">
         <v>2.12</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="14">
         <v>2.67</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="14">
         <v>4.5199999999999996</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="14">
         <v>2.13</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="14">
         <v>2.95</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="14">
         <v>5.2</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="14">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>46157</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>46157</v>
       </c>
-      <c r="C6" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="C6" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="14">
         <v>0.75</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="14">
         <v>0.9</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="14">
         <v>2.12</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="14">
         <v>2.67</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="14">
         <v>4.5199999999999996</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="14">
         <v>2.13</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="14">
         <v>2.95</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="14">
         <v>5.2</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="14">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46178</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <v>46178</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="C7" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="14">
         <v>0.75</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="14">
         <v>0.9</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="14">
         <v>2.12</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="14">
         <v>2.67</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="14">
         <v>4.5199999999999996</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="14">
         <v>2.13</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="14">
         <v>2.95</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="14">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0.85</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14">
+        <v>2.12</v>
+      </c>
+      <c r="H8" s="14">
+        <v>2.67</v>
+      </c>
+      <c r="I8" s="14">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="J8" s="14">
+        <v>2.13</v>
+      </c>
+      <c r="K8" s="14">
+        <v>2.95</v>
+      </c>
+      <c r="L8" s="14">
         <v>5.2</v>
       </c>
     </row>
@@ -1629,249 +1804,278 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE236D12-0519-456D-89C0-C829EF6FE190}">
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="7"/>
-    <col min="22" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="9.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="14"/>
+    <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14">
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>46028</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>46028</v>
       </c>
-      <c r="C2" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12">
         <v>0.45</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="12">
         <v>0.81</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="12">
         <v>0.8</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="12">
         <v>1.1200000000000001</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="12">
         <v>1.1100000000000001</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="14">
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>46064</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="9">
         <v>46064</v>
       </c>
-      <c r="C3" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12">
         <v>0.45</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="12">
         <v>0.83</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="12">
         <v>0.82</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="12">
         <v>1.1399999999999999</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="12">
         <v>1.1200000000000001</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="14">
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>46090</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>46090</v>
       </c>
-      <c r="C4" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="12">
         <v>0.45</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="12">
         <v>0.83</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="12">
         <v>0.82</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="12">
         <v>1.1399999999999999</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="12">
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="14">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>46125</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>46125</v>
       </c>
-      <c r="C5" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="C5" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="14">
         <v>0.45</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="14">
         <v>0.85</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="14">
         <v>0.83</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="14">
         <v>1.1499999999999999</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="14">
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="14">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>46157</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>46157</v>
       </c>
-      <c r="C6" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="C6" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="14">
         <v>0.45</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="14">
         <v>0.85</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="14">
         <v>0.83</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="14">
         <v>1.1499999999999999</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="14">
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="14">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46178</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <v>46178</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="C7" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="14">
         <v>0.45</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="14">
         <v>0.87</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="14">
         <v>0.85</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="14">
         <v>1.18</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="14">
         <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0.45</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0.88</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0.86</v>
+      </c>
+      <c r="H8" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I8" s="14">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>
@@ -1882,230 +2086,256 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B864B0A-C2A5-4EA0-8D10-4C40685755EC}">
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="7"/>
-    <col min="22" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="12.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="14"/>
+    <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>46028</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>46028</v>
       </c>
-      <c r="C2" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12">
         <v>17.03</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="12">
         <v>3.47</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="12">
         <v>3.33</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="12">
         <v>5.3</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="14">
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>46064</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="9">
         <v>46064</v>
       </c>
-      <c r="C3" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12">
         <v>15.31</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="12">
         <v>3.53</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="12">
         <v>3.5</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="12">
         <v>5.4</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="14">
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>46090</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>46090</v>
       </c>
-      <c r="C4" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="7">
+      <c r="C4" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="14">
         <v>12.89</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="14">
         <v>3.3</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="14">
         <v>3.23</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="14">
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="14">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>46125</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>46125</v>
       </c>
-      <c r="C5" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="C5" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="14">
         <v>11.21</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="14">
         <v>3.17</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="14">
         <v>3.1</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="14">
         <v>4.7</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="14">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>46157</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>46157</v>
       </c>
-      <c r="C6" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="C6" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="14">
         <v>10.199999999999999</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="14">
         <v>3.03</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="14">
         <v>2.94</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="14">
         <v>4.45</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="14">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46178</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <v>46178</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="C7" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="14">
         <v>10.89</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="14">
         <v>2.93</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="14">
         <v>2.87</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="14">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="14">
+        <v>11.23</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2.93</v>
+      </c>
+      <c r="G8" s="14">
+        <v>2.87</v>
+      </c>
+      <c r="H8" s="14">
         <v>4.3499999999999996</v>
       </c>
     </row>
@@ -2117,304 +2347,342 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64F3CCF-5660-444E-BF2D-168013FA393D}">
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="21" width="9" style="7"/>
-    <col min="22" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="12.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="21" width="9" style="14"/>
+    <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="H1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14">
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>46028</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>46028</v>
       </c>
-      <c r="C2" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="C2" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="15">
         <v>1415</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="12">
         <v>10.3</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="12">
         <v>9.18</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="12">
         <v>41.44</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="12">
         <v>35.51</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="12">
         <v>9.2100000000000009</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="12">
         <v>12.36</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="12">
         <v>2.75</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="14">
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>46064</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="9">
         <v>46064</v>
       </c>
-      <c r="C3" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="11">
+      <c r="C3" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="15">
         <v>1977</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="12">
         <v>15.25</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="12">
         <v>14.72</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="12">
         <v>45.09</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="12">
         <v>36.79</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="12">
         <v>9.48</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="12">
         <v>14.69</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="12">
         <v>3.04</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="14">
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>46090</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>46090</v>
       </c>
-      <c r="C4" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="12">
+      <c r="C4" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="16">
         <v>2056</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="14">
         <v>14.97</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="14">
         <v>15.52</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="14">
         <v>42.7</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="14">
         <v>37.130000000000003</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="14">
         <v>9.61</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="14">
         <v>14.16</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="14">
         <v>3.24</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="14">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>46125</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>46125</v>
       </c>
-      <c r="C5" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="C5" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="16">
         <v>2221</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="14">
         <v>15.67</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="14">
         <v>15.29</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="14">
         <v>42.91</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="14">
         <v>37.07</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="14">
         <v>9.59</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="14">
         <v>13.94</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="14">
         <v>3.21</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="14">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>46157</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>46157</v>
       </c>
-      <c r="C6" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="12">
+      <c r="C6" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="16">
         <v>2377</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="14">
         <v>16.600000000000001</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="14">
         <v>15.96</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="14">
         <v>41.46</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="14">
         <v>36.729999999999997</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="14">
         <v>9.5500000000000007</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="14">
         <v>14.19</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="14">
         <v>3.21</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="14">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46178</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <v>46178</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="12">
+      <c r="C7" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="16">
         <v>2755</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="14">
         <v>18.68</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="14">
         <v>17.91</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="14">
         <v>42.55</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="14">
         <v>35.979999999999997</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="14">
         <v>9.48</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="14">
         <v>14.61</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="14">
         <v>3.37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="16">
+        <v>2388</v>
+      </c>
+      <c r="F8" s="14">
+        <v>16.53</v>
+      </c>
+      <c r="G8" s="14">
+        <v>15.8</v>
+      </c>
+      <c r="H8" s="14">
+        <v>39.51</v>
+      </c>
+      <c r="I8" s="14">
+        <v>34.86</v>
+      </c>
+      <c r="J8" s="14">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="K8" s="14">
+        <v>13.6</v>
+      </c>
+      <c r="L8" s="14">
+        <v>3.35</v>
       </c>
     </row>
   </sheetData>
@@ -2425,196 +2693,216 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9B3F37-91A5-425D-8E2F-CBD919F64D9B}">
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="21" width="9" style="7"/>
-    <col min="22" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="12.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="21" width="9" style="14"/>
+    <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14">
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>46028</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>46028</v>
       </c>
-      <c r="C2" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12">
         <v>1.9</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="12">
         <v>1.5</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="14">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>46064</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="9">
         <v>46064</v>
       </c>
-      <c r="C3" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12">
         <v>1.9</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="12">
         <v>1.45</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="14">
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>46090</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>46090</v>
       </c>
-      <c r="C4" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="7">
+      <c r="C4" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="14">
         <v>1.9</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="14">
         <v>1.45</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="14">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>46125</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>46125</v>
       </c>
-      <c r="C5" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="C5" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="14">
         <v>1.95</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="14">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="14">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>46157</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>46157</v>
       </c>
-      <c r="C6" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="C6" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="14">
         <v>2</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="14">
         <v>1.55</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="14">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46178</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <v>46178</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="C7" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="14">
         <v>2</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="14">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46209</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -2626,295 +2914,295 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940B0638-7F42-42A0-B176-F348356A0E0B}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="68" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="32.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="10"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="3"/>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="10"/>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="10"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="10"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="10"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="10"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="10"/>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="10"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="3"/>
       <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="10"/>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="10"/>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="3"/>
       <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="10"/>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="3"/>
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="10"/>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="10"/>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="10"/>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="3"/>
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="10"/>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="3"/>
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="10"/>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="3"/>
       <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="10"/>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="3"/>
       <c r="B21" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="10"/>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="10"/>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3"/>
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="10"/>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="3"/>
       <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="10"/>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3"/>
       <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="10"/>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="3"/>
       <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="10" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="10"/>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
       <c r="B28" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="10"/>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
       <c r="B29" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="10"/>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="3"/>
       <c r="B30" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="10"/>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="3"/>
       <c r="B31" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="10" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="10"/>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3"/>
       <c r="B33" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="10"/>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3"/>
       <c r="B34" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="10"/>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3"/>
       <c r="B35" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="10" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="10"/>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="3"/>
       <c r="B37" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="10"/>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3"/>
       <c r="B38" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="10"/>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3"/>
       <c r="B39" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="10"/>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3"/>
       <c r="B40" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="10"/>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
       <c r="B41" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="10"/>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
       <c r="B42" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="10"/>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
       <c r="B43" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="10" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="10"/>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3"/>
       <c r="B45" s="1" t="s">
         <v>58</v>
       </c>

--- a/data_lake/industry/TrendForce/Li-Ion Battery.xlsx
+++ b/data_lake/industry/TrendForce/Li-Ion Battery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07596609-5EA9-4EAF-A6D2-C94B4060BF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A7A542-2468-534C-BAFE-5388455D0484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Battery Cell &amp; Pack" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="71">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -336,23 +336,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -365,7 +365,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -421,7 +421,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -434,10 +434,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -447,28 +447,28 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -746,18 +746,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.09765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="14"/>
     <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="8" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -797,7 +797,7 @@
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="9">
         <v>46028</v>
       </c>
@@ -842,7 +842,7 @@
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="9">
         <v>46064</v>
       </c>
@@ -887,7 +887,7 @@
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="9">
         <v>46090</v>
       </c>
@@ -922,7 +922,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="9">
         <v>46125</v>
       </c>
@@ -957,7 +957,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="9">
         <v>46157</v>
       </c>
@@ -992,7 +992,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="9">
         <v>46178</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="9">
         <v>46209</v>
       </c>
@@ -1059,6 +1059,41 @@
         <v>0.76</v>
       </c>
       <c r="K8" s="14">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0.39</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0.61</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0.38</v>
+      </c>
+      <c r="I9" s="14">
+        <v>0.84</v>
+      </c>
+      <c r="J9" s="14">
+        <v>0.77</v>
+      </c>
+      <c r="K9" s="14">
         <v>0.51</v>
       </c>
     </row>
@@ -1071,19 +1106,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93A7413-903B-41E3-BDE3-CD88FC030C93}">
-  <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="9.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="9.1640625" style="14" bestFit="1" customWidth="1"/>
     <col min="15" max="21" width="9" style="14"/>
     <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="8" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1129,7 +1164,7 @@
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="9">
         <v>46028</v>
       </c>
@@ -1180,7 +1215,7 @@
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="9">
         <v>46064</v>
       </c>
@@ -1231,7 +1266,7 @@
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="9">
         <v>46090</v>
       </c>
@@ -1275,7 +1310,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="9">
         <v>46125</v>
       </c>
@@ -1319,7 +1354,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="9">
         <v>46157</v>
       </c>
@@ -1363,7 +1398,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="9">
         <v>46178</v>
       </c>
@@ -1407,7 +1442,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="9">
         <v>46209</v>
       </c>
@@ -1449,6 +1484,50 @@
       </c>
       <c r="N8" s="14">
         <v>6.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="14">
+        <v>1.53</v>
+      </c>
+      <c r="F9" s="14">
+        <v>10.18</v>
+      </c>
+      <c r="G9" s="14">
+        <v>9.94</v>
+      </c>
+      <c r="H9" s="14">
+        <v>11.66</v>
+      </c>
+      <c r="I9" s="14">
+        <v>17.829999999999998</v>
+      </c>
+      <c r="J9" s="14">
+        <v>18.23</v>
+      </c>
+      <c r="K9" s="14">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="L9" s="14">
+        <v>5.71</v>
+      </c>
+      <c r="M9" s="14">
+        <v>35.979999999999997</v>
+      </c>
+      <c r="N9" s="14">
+        <v>5.76</v>
       </c>
     </row>
   </sheetData>
@@ -1459,18 +1538,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0866DC8-FCF3-4C5E-83C2-1F3B814AC134}">
-  <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="14"/>
     <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="8" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1512,7 +1591,7 @@
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="9">
         <v>46028</v>
       </c>
@@ -1559,7 +1638,7 @@
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="9">
         <v>46064</v>
       </c>
@@ -1606,7 +1685,7 @@
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="9">
         <v>46090</v>
       </c>
@@ -1644,7 +1723,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="9">
         <v>46125</v>
       </c>
@@ -1682,7 +1761,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="9">
         <v>46157</v>
       </c>
@@ -1720,7 +1799,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="9">
         <v>46178</v>
       </c>
@@ -1758,7 +1837,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="9">
         <v>46209</v>
       </c>
@@ -1793,6 +1872,44 @@
         <v>2.95</v>
       </c>
       <c r="L8" s="14">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0.85</v>
+      </c>
+      <c r="F9" s="14">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14">
+        <v>2.12</v>
+      </c>
+      <c r="H9" s="14">
+        <v>2.67</v>
+      </c>
+      <c r="I9" s="14">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="J9" s="14">
+        <v>2.13</v>
+      </c>
+      <c r="K9" s="14">
+        <v>2.95</v>
+      </c>
+      <c r="L9" s="14">
         <v>5.2</v>
       </c>
     </row>
@@ -1804,18 +1921,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE236D12-0519-456D-89C0-C829EF6FE190}">
-  <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="14"/>
     <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="8" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1851,7 +1968,7 @@
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="9">
         <v>46028</v>
       </c>
@@ -1892,7 +2009,7 @@
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="9">
         <v>46064</v>
       </c>
@@ -1933,7 +2050,7 @@
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="9">
         <v>46090</v>
       </c>
@@ -1962,7 +2079,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="9">
         <v>46125</v>
       </c>
@@ -1991,7 +2108,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="9">
         <v>46157</v>
       </c>
@@ -2020,7 +2137,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="9">
         <v>46178</v>
       </c>
@@ -2049,7 +2166,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="9">
         <v>46209</v>
       </c>
@@ -2075,6 +2192,35 @@
         <v>1.2</v>
       </c>
       <c r="I8" s="14">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0.45</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0.88</v>
+      </c>
+      <c r="H9" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I9" s="14">
         <v>1.18</v>
       </c>
     </row>
@@ -2086,18 +2232,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B864B0A-C2A5-4EA0-8D10-4C40685755EC}">
-  <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="14"/>
     <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="8" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2131,7 +2277,7 @@
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="9">
         <v>46028</v>
       </c>
@@ -2170,7 +2316,7 @@
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="9">
         <v>46064</v>
       </c>
@@ -2209,7 +2355,7 @@
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="9">
         <v>46090</v>
       </c>
@@ -2235,7 +2381,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="9">
         <v>46125</v>
       </c>
@@ -2261,7 +2407,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="9">
         <v>46157</v>
       </c>
@@ -2287,7 +2433,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="9">
         <v>46178</v>
       </c>
@@ -2313,7 +2459,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="9">
         <v>46209</v>
       </c>
@@ -2336,6 +2482,32 @@
         <v>2.87</v>
       </c>
       <c r="H8" s="14">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="14">
+        <v>10.01</v>
+      </c>
+      <c r="F9" s="14">
+        <v>2.97</v>
+      </c>
+      <c r="G9" s="14">
+        <v>2.9</v>
+      </c>
+      <c r="H9" s="14">
         <v>4.3499999999999996</v>
       </c>
     </row>
@@ -2347,19 +2519,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64F3CCF-5660-444E-BF2D-168013FA393D}">
-  <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" style="16" bestFit="1" customWidth="1"/>
     <col min="6" max="21" width="9" style="14"/>
     <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="8" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2401,7 +2573,7 @@
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="9">
         <v>46028</v>
       </c>
@@ -2448,7 +2620,7 @@
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="9">
         <v>46064</v>
       </c>
@@ -2495,7 +2667,7 @@
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="9">
         <v>46090</v>
       </c>
@@ -2533,7 +2705,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="9">
         <v>46125</v>
       </c>
@@ -2571,7 +2743,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="9">
         <v>46157</v>
       </c>
@@ -2609,7 +2781,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="9">
         <v>46178</v>
       </c>
@@ -2647,7 +2819,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="9">
         <v>46209</v>
       </c>
@@ -2683,6 +2855,44 @@
       </c>
       <c r="L8" s="14">
         <v>3.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="16">
+        <v>2195</v>
+      </c>
+      <c r="F9" s="14">
+        <v>15.32</v>
+      </c>
+      <c r="G9" s="14">
+        <v>14.86</v>
+      </c>
+      <c r="H9" s="14">
+        <v>36.61</v>
+      </c>
+      <c r="I9" s="14">
+        <v>32.69</v>
+      </c>
+      <c r="J9" s="14">
+        <v>8.48</v>
+      </c>
+      <c r="K9" s="14">
+        <v>13.04</v>
+      </c>
+      <c r="L9" s="14">
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>
@@ -2693,10 +2903,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9B3F37-91A5-425D-8E2F-CBD919F64D9B}">
-  <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" style="11" bestFit="1" customWidth="1"/>
@@ -2705,7 +2915,7 @@
     <col min="22" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="8" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2735,7 +2945,7 @@
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="9">
         <v>46028</v>
       </c>
@@ -2770,7 +2980,7 @@
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="9">
         <v>46064</v>
       </c>
@@ -2805,7 +3015,7 @@
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="9">
         <v>46090</v>
       </c>
@@ -2825,7 +3035,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="9">
         <v>46125</v>
       </c>
@@ -2845,7 +3055,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="9">
         <v>46157</v>
       </c>
@@ -2865,7 +3075,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="9">
         <v>46178</v>
       </c>
@@ -2885,7 +3095,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="9">
         <v>46209</v>
       </c>
@@ -2902,6 +3112,26 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="F8" s="14">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46241</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="F9" s="14">
         <v>1.6</v>
       </c>
     </row>
@@ -2914,19 +3144,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940B0638-7F42-42A0-B176-F348356A0E0B}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="32.5" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="B1" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>60</v>
       </c>
@@ -2937,43 +3167,43 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -2981,61 +3211,61 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" s="3"/>
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" s="3"/>
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
         <v>62</v>
       </c>
@@ -3043,49 +3273,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" s="3"/>
       <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" s="3"/>
       <c r="B21" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="3"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" s="3"/>
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="3"/>
       <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" s="3"/>
       <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" s="3"/>
       <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
         <v>63</v>
       </c>
@@ -3093,31 +3323,31 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" s="3"/>
       <c r="B28" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2">
       <c r="A29" s="3"/>
       <c r="B29" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30" s="3"/>
       <c r="B30" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31" s="3"/>
       <c r="B31" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
         <v>64</v>
       </c>
@@ -3125,25 +3355,25 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" s="3"/>
       <c r="B33" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" s="3"/>
       <c r="B34" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" s="3"/>
       <c r="B35" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
         <v>65</v>
       </c>
@@ -3151,49 +3381,49 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" s="3"/>
       <c r="B37" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" s="3"/>
       <c r="B38" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" s="3"/>
       <c r="B39" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" s="3"/>
       <c r="B40" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2">
       <c r="A41" s="3"/>
       <c r="B41" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42" s="3"/>
       <c r="B42" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2">
       <c r="A43" s="3"/>
       <c r="B43" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" s="3" t="s">
         <v>66</v>
       </c>
@@ -3201,7 +3431,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2">
       <c r="A45" s="3"/>
       <c r="B45" s="1" t="s">
         <v>58</v>
